--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_6_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_6_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>18.8</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>45.79</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>32.87</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>168.4106</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>108.776</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>64.59</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>59.6346</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>35.41</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2161,11 +2161,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>168.4986</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2284,6 +2284,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2492,6 +2493,7 @@
       <c r="F15" s="17" t="inlineStr"/>
       <c r="G15" s="17" t="inlineStr"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -2538,6 +2540,7 @@
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="96" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -2827,11 +2830,11 @@
       </c>
       <c r="B14" s="33">
         <f>SUM(B10:B13)</f>
-        <v/>
+        <v>315.62</v>
       </c>
       <c r="C14" s="23">
         <f>SUM(C10:C13)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -2841,19 +2844,19 @@
       <c r="E14" s="17" t="inlineStr"/>
       <c r="F14" s="17">
         <f>ROUND(AVERAGE(F10:F13),2)</f>
-        <v/>
+        <v>22.48</v>
       </c>
       <c r="G14" s="22">
         <f>ROUND(AVERAGE(G10:G13),4)</f>
-        <v/>
+        <v>0.4118</v>
       </c>
       <c r="H14" s="23">
         <f>ROUND(AVERAGE(H10:H13),2)</f>
-        <v/>
+        <v>29.74</v>
       </c>
       <c r="I14" s="23">
         <f>ROUND(AVERAGE(I10:I13),2)</f>
-        <v/>
+        <v>56.95</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
